--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT1899</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM7316-11566</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL1549608_T_WGS</t>
+          <t>AL_0000025_T_CITE</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>GCAT</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">

--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -2461,7 +2461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ1"/>
+  <dimension ref="A1:BK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2526,6 +2526,7 @@
     <col width="24" customWidth="1" min="60" max="60"/>
     <col width="24" customWidth="1" min="61" max="61"/>
     <col width="24" customWidth="1" min="62" max="62"/>
+    <col width="24" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2656,192 +2657,197 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>chain_type</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_offset</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_size</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>target_cell_number</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="20">
+  <dataValidations count="19">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2857,50 +2863,47 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$9</formula1>
-    </dataValidation>
-    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$5</formula1>
+    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$9</formula1>
+      <formula1>'Lists'!$I$2:$I$5</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$6</formula1>
+      <formula1>'Lists'!$J$2:$J$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$4</formula1>
+    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$6</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$N$2:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$O$2:$O$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$6</formula1>
+    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$4</formula1>
+    <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$R$2:$R$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BD2:BD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2913,7 +2916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,65 +2957,60 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>chain_type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>chain_type</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>is_adapter_trimmed</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3056,37 +3054,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Complete Genomics</t>
+          <t>CITE-Seq</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CITE-Seq</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Affinity Enrichment</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Affinity Enrichment</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>gex</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gex</t>
+          <t>TCRa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>TCRa</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3096,25 +3094,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3153,37 +3146,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>scTCR-Seq</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>scTCR-Seq</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Hybrid Selection</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hybrid Selection</t>
+          <t>Unstranded</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Unstranded</t>
+          <t>vdj</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vdj</t>
+          <t>TCRb</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>TCRb</t>
+          <t>index2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -3193,25 +3186,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>index2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3245,37 +3233,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ion Torrent</t>
+          <t>scBCR-Seq</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>scBCR-Seq</t>
+          <t>scTCR-Seq</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>scTCR-Seq</t>
+          <t>miRNA Size Fractionation</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>miRNA Size Fractionation</t>
+          <t>First Stranded</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>First Stranded</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>IGH</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>IGH</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -3285,15 +3273,10 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3325,37 +3308,32 @@
           <t>SHA512</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>LS454</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>scBCR-Seq</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>scBCR-Seq</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PCR</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>Second Stranded</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IGK</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>IGK</t>
+          <t>read2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>read2</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
@@ -3387,32 +3365,27 @@
           <t>ETag</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SOLiD</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>Not Applicable</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3434,12 +3407,7 @@
           <t>GVCF</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ONT</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3461,12 +3429,7 @@
           <t>VCF</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DNBSEQ</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3488,12 +3451,7 @@
           <t>TBI</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">

--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1262,20 +1262,24 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1283,7 +1287,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1292,17 +1296,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1322,7 +1326,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1332,14 +1336,10 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1366,18 +1366,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1386,7 +1390,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1396,31 +1400,27 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
+          <t>529600</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1430,10 +1430,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1441,26 +1445,26 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>MD5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1480,24 +1484,20 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1514,32 +1514,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1548,32 +1548,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>"CITE-Seq", "scTCR-Seq", "scBCR-Seq"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>CITE-Seq</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>end_bias</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>"3'-end", "5'-end", "Full-length"</t>
+          <t>The sequencing strategy used to generate the data file.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>The end of the cDNA molecule that is preferentially sequenced.</t>
+          <t>"CITE-Seq", "scTCR-Seq", "scBCR-Seq"</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Full-length</t>
+          <t>CITE-Seq</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>end_bias</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Specify the library modality (GEX vs ADT) in CITE-seq, or BCR/TCR for TCR/BCR-seq</t>
+          <t>"3'-end", "5'-end", "Full-length"</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>"GEX", "ADT", "scTCR-Seq", "scBCR-Seq"</t>
+          <t>The end of the cDNA molecule that is preferentially sequenced.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Full-length</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Library selection method.</t>
+          <t>Specify the library modality (GEX vs ADT) in CITE-seq, or BCR/TCR for TCR/BCR-seq</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
+          <t>"GEX", "ADT", "scTCR-Seq", "scBCR-Seq"</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness.</t>
+          <t>Library selection method.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1728,10 +1728,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>The library construction method including version.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>Library strandedness.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1739,7 +1743,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10X V3</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1748,7 +1752,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1758,14 +1762,10 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>10x Feature Barcode Technology for cellranger-multi (ADT is a type of ab(antibody profiling)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>"gex", "vdj", "ab"</t>
-        </is>
-      </c>
+          <t>The library construction method including version.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>10X V3</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>chain_type</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Immune receptor chain the library captures.TCRa/TCRb for TCR, IGH/IGK/IGL for BCR.</t>
+          <t>10x Feature Barcode Technology for cellranger-multi (ADT is a type of ab(antibody profiling)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>"TCRa", "TCRb", "IGH", "IGK", "IGL"</t>
+          <t>"gex", "vdj", "ab"</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1816,28 +1816,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>chain_type</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Immune receptor chain the library captures.TCRa/TCRb for TCR, IGH/IGK/IGL for BCR.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"TCRa", "TCRb", "IGH", "IGK", "IGL"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1846,32 +1850,28 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1890,18 +1890,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1910,7 +1914,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1920,7 +1924,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>The length of the UMI barcode sequence.</t>
+          <t>The offset in sequence of the UMI barcode.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -1931,7 +1935,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1940,71 +1944,71 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_read</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
+          <t>UMI_barcode_size</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>The type of read that contains the cell barcode.</t>
-        </is>
-      </c>
+          <t>The length of the UMI barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>read2</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_offset</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>cell_barcode_read</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cell barcode.</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>The type of read that contains the cell barcode.</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>read2</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_size</t>
+          <t>cell_barcode_offset</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2014,7 +2018,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The length of the cell barcode sequence.</t>
+          <t>The offset in sequence of the cell barcode.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2025,7 +2029,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2034,7 +2038,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>cell_barcode_size</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2044,22 +2048,18 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the cell barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2078,18 +2078,22 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2098,7 +2102,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2108,22 +2112,18 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>The offset in sequence of the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2132,32 +2132,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If fastq/bam files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2176,10 +2176,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2196,7 +2200,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2206,7 +2210,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2217,7 +2221,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2226,7 +2230,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2236,22 +2240,18 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2270,18 +2270,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2290,7 +2294,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>target_cell_number</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2300,18 +2304,18 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Target number of cells to recover for the assay.</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2320,28 +2324,28 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>target_cell_number</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Target number of cells to recover for the assay.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2350,7 +2354,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2360,22 +2364,18 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2394,31 +2394,31 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2439,18 +2439,52 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2847,7 +2881,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="19">
+  <dataValidations count="21">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
@@ -2863,47 +2897,53 @@
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$20</formula1>
     </dataValidation>
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$8</formula1>
+    </dataValidation>
     <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$26</formula1>
+      <formula1>'Lists'!$G$2:$G$26</formula1>
     </dataValidation>
     <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$6</formula1>
+      <formula1>'Lists'!$H$2:$H$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$9</formula1>
     </dataValidation>
     <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$4</formula1>
+      <formula1>'Lists'!$J$2:$J$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$5</formula1>
+      <formula1>'Lists'!$K$2:$K$5</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$9</formula1>
+      <formula1>'Lists'!$L$2:$L$9</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$6</formula1>
+      <formula1>'Lists'!$M$2:$M$6</formula1>
     </dataValidation>
     <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$4</formula1>
+      <formula1>'Lists'!$N$2:$N$4</formula1>
     </dataValidation>
     <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$6</formula1>
+      <formula1>'Lists'!$O$2:$O$6</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$6</formula1>
+      <formula1>'Lists'!$P$2:$P$6</formula1>
     </dataValidation>
     <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$6</formula1>
+      <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
     <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$4</formula1>
+      <formula1>'Lists'!$R$2:$R$4</formula1>
     </dataValidation>
     <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$Q$2:$Q$4</formula1>
+      <formula1>'Lists'!$S$2:$S$4</formula1>
     </dataValidation>
     <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$3</formula1>
+      <formula1>'Lists'!$T$2:$T$3</formula1>
     </dataValidation>
     <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$S$2:$S$3</formula1>
+      <formula1>'Lists'!$U$2:$U$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2916,7 +2956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2947,70 +2987,80 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>chain_type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3044,70 +3094,80 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Complete Genomics</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>CITE-Seq</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>TCRa</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3136,70 +3196,80 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>scTCR-Seq</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>ADT</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>vdj</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>TCRb</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3223,60 +3293,70 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ion Torrent</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>scBCR-Seq</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>scTCR-Seq</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>IGH</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3300,40 +3380,50 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>LS454</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>scBCR-Seq</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>IGK</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
@@ -3357,35 +3447,45 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SOLiD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
@@ -3404,10 +3504,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>sra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ONT</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
@@ -3426,10 +3536,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DNBSEQ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
@@ -3446,12 +3566,17 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -3468,7 +3593,7 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
@@ -3485,7 +3610,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -3502,7 +3627,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -3519,7 +3644,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -3536,7 +3661,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -3548,7 +3673,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -3560,7 +3685,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -3572,7 +3697,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -3584,7 +3709,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -3596,7 +3721,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -3608,49 +3733,49 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -770,20 +770,24 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>cell_entity</t>
+          <t>reported_gender</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The type of single cell entity.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -791,7 +795,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Whole Cell</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -800,7 +804,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>sample_type</t>
+          <t>cell_entity</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -810,14 +814,10 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Text term that represents a description of the kind of tissue collected with respect to disease status</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
-        </is>
-      </c>
+          <t>The type of single cell entity.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -825,7 +825,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Whole Cell</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -834,7 +834,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tumor_descriptor</t>
+          <t>sample_type</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
+          <t>Text term that represents a description of the kind of tissue collected with respect to disease status</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
+          <t>"Tumor", "Normal", "Virus-infected", "Unknown", "Not Reported"</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>composition</t>
+          <t>tumor_descriptor</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tissue type the collected sample comes from</t>
+          <t>Descriptor of tumor status or clinical tumor context for the sample; must be NA for normal samples</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Deceased", "Initial CNS Tumor", "Metastatic", "Post-treatment", "Primary Tumor", "Progressive", "Progressive Disease Post-Mortem", "Recurrence", "Relapse", "Residual", "Second Malignancy", "Unknown", "NA"</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Bone Marrow</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -902,20 +902,24 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>bio_replicate</t>
+          <t>composition</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Label identifying the biological replicate this sample represents</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Tissue type the collected sample comes from</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -923,7 +927,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Rep1</t>
+          <t>Bone Marrow</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -932,7 +936,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>dose_1</t>
+          <t>bio_replicate</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -942,7 +946,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
+          <t>Label identifying the biological replicate this sample represents</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -953,7 +957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10 nM</t>
+          <t>Rep1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -962,7 +966,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>dose_2</t>
+          <t>dose_1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -972,7 +976,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
+          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -983,7 +987,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20 nM</t>
+          <t>10 nM</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -992,7 +996,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>treatment_1</t>
+          <t>dose_2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>temozolomide</t>
+          <t>20 nM</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1022,7 +1026,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>treatment_2</t>
+          <t>treatment_1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1032,7 +1036,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1043,7 +1047,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>temozolomide</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1052,7 +1056,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>cell_line_composition</t>
+          <t>treatment_2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1073,7 +1077,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>DMEM/F12</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1082,7 +1086,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>cell_line_passage</t>
+          <t>cell_line_composition</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1092,18 +1096,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>DMEM/F12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1112,7 +1116,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>timepoint</t>
+          <t>cell_line_passage</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1122,18 +1126,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Timepoint associated with the treatment, collection, or experiment</t>
+          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24h</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1142,7 +1146,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>parental_model_id</t>
+          <t>timepoint</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
+          <t>Timepoint associated with the treatment, collection, or experiment</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1163,7 +1167,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760</t>
+          <t>24h</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1172,7 +1176,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>model_id</t>
+          <t>parental_model_id</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1182,7 +1186,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
+          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1193,7 +1197,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760-mCherry-Luciferase</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1202,7 +1206,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>local_dir_path</t>
+          <t>model_id</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1212,7 +1216,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
+          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1232,7 +1236,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>aws_s3_path</t>
+          <t>local_dir_path</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1242,7 +1246,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1253,7 +1257,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>s3://bucket/prefix</t>
+          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1262,24 +1266,20 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_source_platform</t>
+          <t>aws_s3_path</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Source platform where files are stored and from which they are harmonized</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
-        </is>
-      </c>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>bti_aws</t>
+          <t>s3://bucket/prefix</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1296,20 +1296,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1317,7 +1321,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1326,17 +1330,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1347,7 +1351,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1356,7 +1360,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1366,14 +1370,10 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1400,18 +1400,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1420,7 +1424,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1430,31 +1434,27 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t>529600</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1464,10 +1464,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1475,26 +1479,26 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
+          <t>MD5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -1505,7 +1509,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1514,24 +1518,20 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>instrument_platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1548,32 +1548,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1582,32 +1582,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>"CITE-Seq", "scTCR-Seq", "scBCR-Seq"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>CITE-Seq</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>end_bias</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>"3'-end", "5'-end", "Full-length"</t>
+          <t>The sequencing strategy used to generate the data file.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>The end of the cDNA molecule that is preferentially sequenced.</t>
+          <t>"CITE-Seq", "scTCR-Seq", "scBCR-Seq"</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Full-length</t>
+          <t>CITE-Seq</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>library_type</t>
+          <t>end_bias</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Specify the library modality (GEX vs ADT) in CITE-seq, or BCR/TCR for TCR/BCR-seq</t>
+          <t>"3'-end", "5'-end", "Full-length"</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>"GEX", "ADT", "scTCR-Seq", "scBCR-Seq"</t>
+          <t>The end of the cDNA molecule that is preferentially sequenced.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>Full-length</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>library_type</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Library selection method.</t>
+          <t>Specify the library modality (GEX vs ADT) in CITE-seq, or BCR/TCR for TCR/BCR-seq</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
+          <t>"GEX", "ADT", "scTCR-Seq", "scBCR-Seq"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness.</t>
+          <t>Library selection method.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random","rRNA Depletion", "Other"</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>library_construction</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1762,10 +1762,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>The library construction method including version.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Library strandedness.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1773,7 +1777,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10X V3</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1782,7 +1786,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>feature_type</t>
+          <t>library_construction</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1792,14 +1796,10 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>10x Feature Barcode Technology for cellranger-multi (ADT is a type of ab(antibody profiling)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>"gex", "vdj", "ab"</t>
-        </is>
-      </c>
+          <t>The library construction method including version.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>10X V3</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>chain_type</t>
+          <t>feature_type</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Immune receptor chain the library captures.TCRa/TCRb for TCR, IGH/IGK/IGL for BCR.</t>
+          <t>10x Feature Barcode Technology for cellranger-multi (ADT is a type of ab(antibody profiling)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>"TCRa", "TCRb", "IGH", "IGK", "IGL"</t>
+          <t>"gex", "vdj", "ab"</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1850,28 +1850,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>chain_type</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>Immune receptor chain the library captures.TCRa/TCRb for TCR, IGH/IGK/IGL for BCR.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>"TCRa", "TCRb", "IGH", "IGK", "IGL"</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1880,32 +1884,28 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_read</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>Total number of reads that align to the reference.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>index1</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1914,7 +1914,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_offset</t>
+          <t>UMI_barcode_read</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1924,18 +1924,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the UMI barcode.</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>The type of read that contains the UMI barcode.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>index1</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1944,7 +1948,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>UMI_barcode_size</t>
+          <t>UMI_barcode_offset</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>The length of the UMI barcode sequence.</t>
+          <t>The offset in sequence of the UMI barcode.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -1965,7 +1969,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -1974,71 +1978,71 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_read</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr"/>
+          <t>UMI_barcode_size</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>The type of read that contains the cell barcode.</t>
-        </is>
-      </c>
+          <t>The length of the UMI barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>read2</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_offset</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>cell_barcode_read</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cell barcode.</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>The type of read that contains the cell barcode.</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>read2</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>cell_barcode_size</t>
+          <t>cell_barcode_offset</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2048,7 +2052,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>The length of the cell barcode sequence.</t>
+          <t>The offset in sequence of the cell barcode.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2068,7 +2072,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read</t>
+          <t>cell_barcode_size</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2078,22 +2082,18 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>The type of read that contains the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
-        </is>
-      </c>
+          <t>The length of the cell barcode sequence.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>read1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>cDNA_read_offset</t>
+          <t>cDNA_read</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2112,18 +2112,22 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>The offset in sequence of the cDNA read.</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>The type of read that contains the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>"index1", "index2", "read1", "read2", "Not Applicable"</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>read1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2132,7 +2136,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>cDNA_read_offset</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2142,22 +2146,18 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "NA"</t>
-        </is>
-      </c>
+          <t>The offset in sequence of the cDNA read.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2166,32 +2166,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If fastq/bam files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False", "NA"</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2210,10 +2210,14 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -2221,7 +2225,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2230,7 +2234,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2240,7 +2244,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2251,7 +2255,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2260,7 +2264,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2270,22 +2274,18 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2294,7 +2294,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2304,18 +2304,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2324,7 +2328,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>target_cell_number</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2334,18 +2338,18 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Target number of cells to recover for the assay.</t>
+          <t>Base sequence of the sequencing adapter. Required when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2354,28 +2358,28 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>target_cell_number</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Target number of cells to recover for the assay.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2384,7 +2388,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2394,22 +2398,18 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2428,31 +2428,31 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2473,18 +2473,52 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>RBT</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2495,7 +2529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2561,6 +2595,7 @@
     <col width="24" customWidth="1" min="61" max="61"/>
     <col width="24" customWidth="1" min="62" max="62"/>
     <col width="24" customWidth="1" min="63" max="63"/>
+    <col width="24" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2611,339 +2646,347 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>cell_entity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>bio_replicate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dose_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dose_2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>treatment_1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>treatment_2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>cell_line_composition</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>cell_line_passage</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>parental_model_id</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>model_id</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>local_dir_path</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>aws_s3_path</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>end_bias</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>library_construction</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>chain_type</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_offset</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>UMI_barcode_size</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_read</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_offset</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>cell_barcode_size</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>cDNA_read_offset</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>target_cell_number</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="21">
+  <dataValidations count="22">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$B$2:$B$2</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$6</formula1>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$14</formula1>
+      <formula1>'Lists'!$D$2:$D$6</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$20</formula1>
+      <formula1>'Lists'!$E$2:$E$14</formula1>
     </dataValidation>
-    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$8</formula1>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$26</formula1>
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$8</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$6</formula1>
+    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$9</formula1>
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$4</formula1>
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$5</formula1>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$9</formula1>
+      <formula1>'Lists'!$L$2:$L$5</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$6</formula1>
+      <formula1>'Lists'!$M$2:$M$9</formula1>
     </dataValidation>
-    <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$4</formula1>
+    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$N$2:$N$6</formula1>
     </dataValidation>
     <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$6</formula1>
+      <formula1>'Lists'!$O$2:$O$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$P$2:$P$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$6</formula1>
     </dataValidation>
-    <dataValidation sqref="BA2:BA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$4</formula1>
+    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$R$2:$R$6</formula1>
     </dataValidation>
     <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$S$2:$S$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BE2:BE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$T$2:$T$3</formula1>
+    <dataValidation sqref="BC2:BC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BI2:BI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BF2:BF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$U$2:$U$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="BJ2:BJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$V$2:$V$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2956,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,95 +3015,100 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>sample_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tumor_descriptor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>composition</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>feature_type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>chain_type</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>UMI_barcode_read</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>cDNA_read</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
@@ -3079,95 +3127,100 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Deceased</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Bone Marrow</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>bti_aws</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Complete Genomics</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CITE-Seq</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>GEX</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>gex</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>TCRa</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>index1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3181,95 +3234,100 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Initial CNS Tumor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Buffy Coat</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>local_drive</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Illumina</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>scTCR-Seq</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ADT</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>vdj</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>TCRb</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>index2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3278,504 +3336,509 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
+          <t>Not Reported</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Virus-infected</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Metastatic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Derived Cell Line</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>bti_aws_and_local_drive</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Ion Torrent</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>scBCR-Seq</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>scTCR-Seq</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>IGH</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>read1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Post-treatment</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>cgc</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>LS454</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>scBCR-Seq</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>IGK</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>read2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Primary Tumor</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>kids_first</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SOLiD</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Progressive</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Patient Derived Xenograft</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>sra</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>ONT</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Random</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Progressive Disease Post-Mortem</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Xenograft</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>synapse</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>DNBSEQ</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Recurrence</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Relapse</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Second Malignancy</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Saliva</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
+++ b/excel_templates/single_cell_citeseq_bcrtcr_manifest_template.xlsx
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
